--- a/data/processed_results/experimental_processed_dataset.xlsx
+++ b/data/processed_results/experimental_processed_dataset.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
   <si>
     <t>Column</t>
   </si>
@@ -57,6 +57,12 @@
     <t>SO4</t>
   </si>
   <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
     <t>Br_mM</t>
   </si>
   <si>
@@ -81,10 +87,10 @@
     <t>Outflow_Concentrations</t>
   </si>
   <si>
-    <t>Processed concentrations of NO3, NO2, SO4, DOC, DIC</t>
+    <t>Processed concentrations of NO3, NO2, SO4, DOC, DIC, pH, EC</t>
   </si>
   <si>
-    <t>Time in seconds since t0; Concentrations in mM (corrected for dead volume)</t>
+    <t>Time in seconds since t0; Concentrations in mM (corrected for dead volume); pH (unitless); EC (μS/cm)</t>
   </si>
   <si>
     <t>Bromide_Tracer</t>
@@ -463,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1406,338 +1412,338 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B68">
-        <v>391161.80289477075</v>
+        <v>390837.4996969906</v>
       </c>
       <c r="C68" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D68">
-        <v>0.8928571428571429</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B69">
-        <v>499324.43792375014</v>
+        <v>498814.27751450357</v>
       </c>
       <c r="C69" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D69">
-        <v>0.7374193548387097</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B70">
-        <v>650528.4058831015</v>
+        <v>649993.3199952871</v>
       </c>
       <c r="C70" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D70">
-        <v>0.9241935483870968</v>
+        <v>8.21</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71">
-        <v>823321.7715896445</v>
+        <v>822792.4627580979</v>
       </c>
       <c r="C71" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D71">
-        <v>0.8840322580645161</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B72">
-        <v>888141.3654190782</v>
+        <v>909186.4201351142</v>
       </c>
       <c r="C72" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D72">
-        <v>0.9500000000000001</v>
+        <v>8.22</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B73">
-        <v>909884.189647064</v>
+        <v>1.0820807473374768e6</v>
       </c>
       <c r="C73" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D73">
-        <v>0.9085483870967742</v>
+        <v>8.14</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B74">
-        <v>1.0824443668921639e6</v>
+        <v>1.1684142775145036e6</v>
       </c>
       <c r="C74" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D74">
-        <v>1.0240322580645163</v>
+        <v>8.22</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B75">
-        <v>1.1688729534564952e6</v>
+        <v>1.3411967341129505e6</v>
       </c>
       <c r="C75" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D75">
-        <v>0.9616129032258064</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76">
-        <v>1.2552998145675145e6</v>
+        <v>1.5139732193397437e6</v>
       </c>
       <c r="C76" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D76">
-        <v>1.0785714285714285</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B77">
-        <v>1.3200962798196336e6</v>
+        <v>1.6867767737286591e6</v>
       </c>
       <c r="C77" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D77">
-        <v>1.1043548387096773</v>
+        <v>8.12</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B78">
-        <v>1.5144825795838374e6</v>
+        <v>1.7732001246849748e6</v>
       </c>
       <c r="C78" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D78">
-        <v>1.0071428571428571</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B79">
-        <v>1.5576774223094333e6</v>
+        <v>2.053993319995287e6</v>
       </c>
       <c r="C79" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D79">
-        <v>1.0</v>
+        <v>8.12</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80">
-        <v>1.5792781627590072e6</v>
+        <v>390837.4996969906</v>
       </c>
       <c r="C80" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D80">
-        <v>0.7785714285714286</v>
+        <v>678.0</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B81">
-        <v>1.6008691948139973e6</v>
+        <v>498814.27751450357</v>
       </c>
       <c r="C81" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D81">
-        <v>0.5128571428571428</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B82">
-        <v>1.622472204259068e6</v>
+        <v>649993.3199952871</v>
       </c>
       <c r="C82" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D82">
-        <v>0.49193548387096775</v>
+        <v>991.0</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83">
-        <v>1.6872774223094333e6</v>
+        <v>822792.4627580979</v>
       </c>
       <c r="C83" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D83">
-        <v>0.48142857142857143</v>
+        <v>852.0</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B84">
-        <v>1.7736884005452667e6</v>
+        <v>909186.4201351142</v>
       </c>
       <c r="C84" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D84">
-        <v>0.5178571428571429</v>
+        <v>924.0</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B85">
-        <v>1.8384927160031025e6</v>
+        <v>1.0820807473374768e6</v>
       </c>
       <c r="C85" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D85">
-        <v>0.5235714285714286</v>
+        <v>897.0</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B86">
-        <v>1.9464811122164773e6</v>
+        <v>1.1684142775145036e6</v>
       </c>
       <c r="C86" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D86">
-        <v>0.5411290322580645</v>
+        <v>866.0</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B87">
-        <v>2.0544912822568144e6</v>
+        <v>1.3411967341129505e6</v>
       </c>
       <c r="C87" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D87">
-        <v>0.5459677419354839</v>
+        <v>855.0</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B88">
-        <v>2.0835631145066095e6</v>
+        <v>1.5139732193397437e6</v>
       </c>
       <c r="C88" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D88">
-        <v>0.5285714285714286</v>
+        <v>832.0</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B89">
-        <v>2.112360813009184e6</v>
+        <v>1.6867767737286591e6</v>
       </c>
       <c r="C89" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D89">
-        <v>0.1657142857142857</v>
+        <v>773.0</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B90">
-        <v>2.140780254133058e6</v>
+        <v>1.7732001246849748e6</v>
       </c>
       <c r="C90" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D90">
-        <v>0.062</v>
+        <v>757.0</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B91">
-        <v>2.1555833114378825e6</v>
+        <v>2.053993319995287e6</v>
       </c>
       <c r="C91" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D91">
-        <v>0.028</v>
+        <v>715.0</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1745,13 +1751,13 @@
         <v>2</v>
       </c>
       <c r="B92">
-        <v>2.2140233114378825e6</v>
+        <v>391161.80289477075</v>
       </c>
       <c r="C92" t="s">
         <v>4</v>
       </c>
       <c r="D92">
-        <v>0.018142857142857145</v>
+        <v>0.8928571428571429</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1759,13 +1765,13 @@
         <v>2</v>
       </c>
       <c r="B93">
-        <v>2.30761556575243e6</v>
+        <v>499324.43792375014</v>
       </c>
       <c r="C93" t="s">
         <v>4</v>
       </c>
       <c r="D93">
-        <v>0.022857142857142857</v>
+        <v>0.7374193548387097</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1773,13 +1779,13 @@
         <v>2</v>
       </c>
       <c r="B94">
-        <v>574936.875612625</v>
+        <v>650528.4058831015</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D94">
-        <v>0.16333333333333333</v>
+        <v>0.9241935483870968</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1787,13 +1793,13 @@
         <v>2</v>
       </c>
       <c r="B95">
-        <v>769321.7715896445</v>
+        <v>823321.7715896445</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D95">
-        <v>0.11333333333333334</v>
+        <v>0.8840322580645161</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1801,13 +1807,13 @@
         <v>2</v>
       </c>
       <c r="B96">
-        <v>1.20126540429158e6</v>
+        <v>888141.3654190782</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96">
-        <v>0.27</v>
+        <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1815,13 +1821,13 @@
         <v>2</v>
       </c>
       <c r="B97">
-        <v>1.4172608130091839e6</v>
+        <v>909884.189647064</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97">
-        <v>0.2041666666666667</v>
+        <v>0.9085483870967742</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1829,13 +1835,13 @@
         <v>2</v>
       </c>
       <c r="B98">
-        <v>1.6548395572947406e6</v>
+        <v>1.0824443668921639e6</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D98">
-        <v>0.06166666666666667</v>
+        <v>1.0240322580645163</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1843,13 +1849,13 @@
         <v>2</v>
       </c>
       <c r="B99">
-        <v>1.870898404133801e6</v>
+        <v>1.1688729534564952e6</v>
       </c>
       <c r="C99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D99">
-        <v>0.059166666666666666</v>
+        <v>0.9616129032258064</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1857,13 +1863,13 @@
         <v>2</v>
       </c>
       <c r="B100">
-        <v>2.0220912822568144e6</v>
+        <v>1.2552998145675145e6</v>
       </c>
       <c r="C100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D100">
-        <v>0.075</v>
+        <v>1.0785714285714285</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1871,13 +1877,13 @@
         <v>2</v>
       </c>
       <c r="B101">
-        <v>574936.875612625</v>
+        <v>1.3200962798196336e6</v>
       </c>
       <c r="C101" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D101">
-        <v>2.625</v>
+        <v>1.1043548387096773</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1885,13 +1891,13 @@
         <v>2</v>
       </c>
       <c r="B102">
-        <v>769321.7715896445</v>
+        <v>1.5144825795838374e6</v>
       </c>
       <c r="C102" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D102">
-        <v>3.2083333333333335</v>
+        <v>1.0071428571428571</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1899,13 +1905,13 @@
         <v>2</v>
       </c>
       <c r="B103">
-        <v>1.20126540429158e6</v>
+        <v>1.5576774223094333e6</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D103">
-        <v>3.408333333333333</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1913,13 +1919,13 @@
         <v>2</v>
       </c>
       <c r="B104">
-        <v>1.4172608130091839e6</v>
+        <v>1.5792781627590072e6</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D104">
-        <v>3.608333333333333</v>
+        <v>0.7785714285714286</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1927,13 +1933,13 @@
         <v>2</v>
       </c>
       <c r="B105">
-        <v>1.6548395572947406e6</v>
+        <v>1.6008691948139973e6</v>
       </c>
       <c r="C105" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D105">
-        <v>3.591666666666667</v>
+        <v>0.5128571428571428</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1941,13 +1947,13 @@
         <v>2</v>
       </c>
       <c r="B106">
-        <v>1.870898404133801e6</v>
+        <v>1.622472204259068e6</v>
       </c>
       <c r="C106" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D106">
-        <v>3.5666666666666664</v>
+        <v>0.49193548387096775</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1955,13 +1961,13 @@
         <v>2</v>
       </c>
       <c r="B107">
-        <v>2.0220912822568144e6</v>
+        <v>1.6872774223094333e6</v>
       </c>
       <c r="C107" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D107">
-        <v>3.641666666666667</v>
+        <v>0.48142857142857143</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1969,13 +1975,13 @@
         <v>2</v>
       </c>
       <c r="B108">
-        <v>391161.80289477075</v>
+        <v>1.7736884005452667e6</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D108">
-        <v>0.9089245755395683</v>
+        <v>0.5178571428571429</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1983,13 +1989,13 @@
         <v>2</v>
       </c>
       <c r="B109">
-        <v>499324.43792375014</v>
+        <v>1.8384927160031025e6</v>
       </c>
       <c r="C109" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D109">
-        <v>0.7548648057553957</v>
+        <v>0.5235714285714286</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1997,13 +2003,13 @@
         <v>2</v>
       </c>
       <c r="B110">
-        <v>650528.4058831015</v>
+        <v>1.9464811122164773e6</v>
       </c>
       <c r="C110" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D110">
-        <v>0.2757059136690648</v>
+        <v>0.5411290322580645</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2011,13 +2017,13 @@
         <v>2</v>
       </c>
       <c r="B111">
-        <v>823321.7715896445</v>
+        <v>2.0544912822568144e6</v>
       </c>
       <c r="C111" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D111">
-        <v>0.20044007194244604</v>
+        <v>0.5459677419354839</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2025,13 +2031,13 @@
         <v>2</v>
       </c>
       <c r="B112">
-        <v>888141.3654190782</v>
+        <v>2.0835631145066095e6</v>
       </c>
       <c r="C112" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D112">
-        <v>0.158103035971223</v>
+        <v>0.5285714285714286</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2039,13 +2045,13 @@
         <v>2</v>
       </c>
       <c r="B113">
-        <v>1.0824443668921639e6</v>
+        <v>2.112360813009184e6</v>
       </c>
       <c r="C113" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D113">
-        <v>0.04418954820143885</v>
+        <v>0.1657142857142857</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2053,13 +2059,13 @@
         <v>2</v>
       </c>
       <c r="B114">
-        <v>1.1688729534564952e6</v>
+        <v>2.140780254133058e6</v>
       </c>
       <c r="C114" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D114">
-        <v>0.01996335539568344</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2067,13 +2073,13 @@
         <v>2</v>
       </c>
       <c r="B115">
-        <v>1.2552998145675145e6</v>
+        <v>2.1555833114378825e6</v>
       </c>
       <c r="C115" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D115">
-        <v>0.00893053525179856</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2081,13 +2087,13 @@
         <v>2</v>
       </c>
       <c r="B116">
-        <v>1.3416962798196336e6</v>
+        <v>2.2140233114378825e6</v>
       </c>
       <c r="C116" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D116">
-        <v>0.014869480575539565</v>
+        <v>0.018142857142857145</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2095,13 +2101,13 @@
         <v>2</v>
       </c>
       <c r="B117">
-        <v>1.5144825795838374e6</v>
+        <v>2.30761556575243e6</v>
       </c>
       <c r="C117" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D117">
-        <v>0.0321571035971223</v>
+        <v>0.022857142857142857</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2109,13 +2115,13 @@
         <v>2</v>
       </c>
       <c r="B118">
-        <v>1.5576774223094333e6</v>
+        <v>574936.875612625</v>
       </c>
       <c r="C118" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D118">
-        <v>0.037508034532374106</v>
+        <v>0.16333333333333333</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2123,13 +2129,13 @@
         <v>2</v>
       </c>
       <c r="B119">
-        <v>1.5792781627590072e6</v>
+        <v>769321.7715896445</v>
       </c>
       <c r="C119" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D119">
-        <v>0.036920020143884895</v>
+        <v>0.11333333333333334</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2137,13 +2143,13 @@
         <v>2</v>
       </c>
       <c r="B120">
-        <v>1.6008691948139973e6</v>
+        <v>1.20126540429158e6</v>
       </c>
       <c r="C120" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D120">
-        <v>0.035391182733812955</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2151,13 +2157,13 @@
         <v>2</v>
       </c>
       <c r="B121">
-        <v>1.622472204259068e6</v>
+        <v>1.4172608130091839e6</v>
       </c>
       <c r="C121" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D121">
-        <v>0.03445035971223022</v>
+        <v>0.2041666666666667</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2165,13 +2171,13 @@
         <v>2</v>
       </c>
       <c r="B122">
-        <v>1.6872774223094333e6</v>
+        <v>1.6548395572947406e6</v>
       </c>
       <c r="C122" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D122">
-        <v>0.035273579856115116</v>
+        <v>0.06166666666666667</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2179,13 +2185,13 @@
         <v>2</v>
       </c>
       <c r="B123">
-        <v>1.7736884005452667e6</v>
+        <v>1.870898404133801e6</v>
       </c>
       <c r="C123" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D123">
-        <v>0.03786084316546764</v>
+        <v>0.059166666666666666</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2193,13 +2199,13 @@
         <v>2</v>
       </c>
       <c r="B124">
-        <v>1.8384927160031025e6</v>
+        <v>2.0220912822568144e6</v>
       </c>
       <c r="C124" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D124">
-        <v>0.03991889352517986</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2207,13 +2213,13 @@
         <v>2</v>
       </c>
       <c r="B125">
-        <v>2.0544912822568144e6</v>
+        <v>574936.875612625</v>
       </c>
       <c r="C125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D125">
-        <v>0.0414477309352518</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2221,13 +2227,13 @@
         <v>2</v>
       </c>
       <c r="B126">
-        <v>499324.43792375014</v>
+        <v>769321.7715896445</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D126">
-        <v>0.015625</v>
+        <v>3.2083333333333335</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2235,13 +2241,13 @@
         <v>2</v>
       </c>
       <c r="B127">
-        <v>650528.4058831015</v>
+        <v>1.20126540429158e6</v>
       </c>
       <c r="C127" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D127">
-        <v>0.013125</v>
+        <v>3.408333333333333</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2249,13 +2255,13 @@
         <v>2</v>
       </c>
       <c r="B128">
-        <v>823321.7715896445</v>
+        <v>1.4172608130091839e6</v>
       </c>
       <c r="C128" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D128">
-        <v>0.012187499999999999</v>
+        <v>3.608333333333333</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2263,13 +2269,13 @@
         <v>2</v>
       </c>
       <c r="B129">
-        <v>909884.189647064</v>
+        <v>1.6548395572947406e6</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D129">
-        <v>0.012499999999999999</v>
+        <v>3.591666666666667</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2277,13 +2283,13 @@
         <v>2</v>
       </c>
       <c r="B130">
-        <v>1.0824443668921639e6</v>
+        <v>1.870898404133801e6</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D130">
-        <v>0.013229166666666667</v>
+        <v>3.5666666666666664</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2291,13 +2297,13 @@
         <v>2</v>
       </c>
       <c r="B131">
-        <v>1.1688729534564952e6</v>
+        <v>2.0220912822568144e6</v>
       </c>
       <c r="C131" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D131">
-        <v>0.012604166666666666</v>
+        <v>3.641666666666667</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2305,13 +2311,13 @@
         <v>2</v>
       </c>
       <c r="B132">
-        <v>1.3200962798196336e6</v>
+        <v>391161.80289477075</v>
       </c>
       <c r="C132" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D132">
-        <v>0.008541666666666666</v>
+        <v>0.9089245755395683</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2319,13 +2325,13 @@
         <v>2</v>
       </c>
       <c r="B133">
-        <v>1.5792781627590072e6</v>
+        <v>499324.43792375014</v>
       </c>
       <c r="C133" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D133">
-        <v>0.016354166666666666</v>
+        <v>0.7548648057553957</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2333,13 +2339,13 @@
         <v>2</v>
       </c>
       <c r="B134">
-        <v>1.622472204259068e6</v>
+        <v>650528.4058831015</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D134">
-        <v>0.012187499999999999</v>
+        <v>0.2757059136690648</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2347,13 +2353,13 @@
         <v>2</v>
       </c>
       <c r="B135">
-        <v>1.8384927160031025e6</v>
+        <v>823321.7715896445</v>
       </c>
       <c r="C135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D135">
-        <v>0.007395833333333333</v>
+        <v>0.20044007194244604</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2361,13 +2367,13 @@
         <v>2</v>
       </c>
       <c r="B136">
-        <v>1.9464811122164773e6</v>
+        <v>888141.3654190782</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136">
-        <v>0.011562500000000002</v>
+        <v>0.158103035971223</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2375,685 +2381,685 @@
         <v>2</v>
       </c>
       <c r="B137">
-        <v>2.0544912822568144e6</v>
+        <v>1.0824443668921639e6</v>
       </c>
       <c r="C137" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D137">
-        <v>0.011874999999999998</v>
+        <v>0.04418954820143885</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B138">
-        <v>391032.08745753707</v>
+        <v>1.1688729534564952e6</v>
       </c>
       <c r="C138" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D138">
-        <v>0.8296774193548386</v>
+        <v>0.01996335539568344</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B139">
-        <v>499224.7790934134</v>
+        <v>1.2552998145675145e6</v>
       </c>
       <c r="C139" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D139">
-        <v>0.8370967741935483</v>
+        <v>0.00893053525179856</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B140">
-        <v>650415.7359801112</v>
+        <v>1.3416962798196336e6</v>
       </c>
       <c r="C140" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D140">
-        <v>0.9064516129032258</v>
+        <v>0.014869480575539565</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B141">
-        <v>823212.6847922642</v>
+        <v>1.5144825795838374e6</v>
       </c>
       <c r="C141" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D141">
-        <v>0.8887096774193549</v>
+        <v>0.0321571035971223</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B142">
-        <v>909615.7359801112</v>
+        <v>1.5576774223094333e6</v>
       </c>
       <c r="C142" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D142">
-        <v>0.8585483870967742</v>
+        <v>0.037508034532374106</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B143">
-        <v>1.0824119190816395e6</v>
+        <v>1.5792781627590072e6</v>
       </c>
       <c r="C143" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D143">
-        <v>1.0806451612903225</v>
+        <v>0.036920020143884895</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B144">
-        <v>1.168767088649534e6</v>
+        <v>1.6008691948139973e6</v>
       </c>
       <c r="C144" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D144">
-        <v>0.9708064516129032</v>
+        <v>0.035391182733812955</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B145">
-        <v>1.2551405049737038e6</v>
+        <v>1.622472204259068e6</v>
       </c>
       <c r="C145" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D145">
-        <v>1.149516129032258</v>
+        <v>0.03445035971223022</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B146">
-        <v>1.341541383546906e6</v>
+        <v>1.6872774223094333e6</v>
       </c>
       <c r="C146" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D146">
-        <v>1.1411290322580645</v>
+        <v>0.035273579856115116</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B147">
-        <v>1.5143226265206872e6</v>
+        <v>1.7736884005452667e6</v>
       </c>
       <c r="C147" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D147">
-        <v>1.0816129032258064</v>
+        <v>0.03786084316546764</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B148">
-        <v>1.557530744903275e6</v>
+        <v>1.8384927160031025e6</v>
       </c>
       <c r="C148" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D148">
-        <v>1.0793548387096774</v>
+        <v>0.03991889352517986</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B149">
-        <v>1.579087933114048e6</v>
+        <v>2.0544912822568144e6</v>
       </c>
       <c r="C149" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D149">
-        <v>0.8554838709677419</v>
+        <v>0.0414477309352518</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B150">
-        <v>1.600714385647834e6</v>
+        <v>499324.43792375014</v>
       </c>
       <c r="C150" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D150">
-        <v>0.6135483870967742</v>
+        <v>0.015625</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B151">
-        <v>1.6223153074353987e6</v>
+        <v>650528.4058831015</v>
       </c>
       <c r="C151" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D151">
-        <v>0.5656451612903226</v>
+        <v>0.013125</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B152">
-        <v>1.6871235345618173e6</v>
+        <v>823321.7715896445</v>
       </c>
       <c r="C152" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D152">
-        <v>0.5512903225806451</v>
+        <v>0.012187499999999999</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B153">
-        <v>1.773541383546906e6</v>
+        <v>909884.189647064</v>
       </c>
       <c r="C153" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D153">
-        <v>0.5954838709677419</v>
+        <v>0.012499999999999999</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B154">
-        <v>1.8383343144673796e6</v>
+        <v>1.0824443668921639e6</v>
       </c>
       <c r="C154" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D154">
-        <v>0.5933870967741935</v>
+        <v>0.013229166666666667</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B155">
-        <v>1.9463226265206872e6</v>
+        <v>1.1688729534564952e6</v>
       </c>
       <c r="C155" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D155">
-        <v>0.6312903225806452</v>
+        <v>0.012604166666666666</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B156">
-        <v>2.0543078896103424e6</v>
+        <v>1.3200962798196336e6</v>
       </c>
       <c r="C156" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D156">
-        <v>0.6196774193548388</v>
+        <v>0.008541666666666666</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B157">
-        <v>2.0834369762544057e6</v>
+        <v>1.5792781627590072e6</v>
       </c>
       <c r="C157" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D157">
-        <v>0.6014285714285714</v>
+        <v>0.016354166666666666</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B158">
-        <v>2.112228951263744e6</v>
+        <v>1.622472204259068e6</v>
       </c>
       <c r="C158" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D158">
-        <v>0.12785714285714286</v>
+        <v>0.012187499999999999</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B159">
-        <v>2.1410069553399715e6</v>
+        <v>1.8384927160031025e6</v>
       </c>
       <c r="C159" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D159">
-        <v>0.105</v>
+        <v>0.007395833333333333</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B160">
-        <v>2.155472910379259e6</v>
+        <v>1.9464811122164773e6</v>
       </c>
       <c r="C160" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D160">
-        <v>0.09714285714285716</v>
+        <v>0.011562500000000002</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B161">
-        <v>2.2138608058982217e6</v>
+        <v>2.0544912822568144e6</v>
       </c>
       <c r="C161" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D161">
-        <v>0.03</v>
+        <v>0.011874999999999998</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B162">
-        <v>2.3074225869580563e6</v>
+        <v>391161.80289477075</v>
       </c>
       <c r="C162" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D162">
-        <v>0.04928571428571428</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B163">
-        <v>574821.031096038</v>
+        <v>499324.43792375014</v>
       </c>
       <c r="C163" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D163">
-        <v>0.10333333333333333</v>
+        <v>8.12</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B164">
-        <v>769181.1158093434</v>
+        <v>650528.4058831015</v>
       </c>
       <c r="C164" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D164">
-        <v>0.11583333333333333</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165">
-        <v>1.2011474935592408e6</v>
+        <v>823321.7715896445</v>
       </c>
       <c r="C165" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D165">
-        <v>0.2708333333333333</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B166">
-        <v>1.4171235345618173e6</v>
+        <v>888141.3654190782</v>
       </c>
       <c r="C166" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D166">
-        <v>0.10416666666666667</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B167">
-        <v>1.6547069553399715e6</v>
+        <v>1.0824443668921639e6</v>
       </c>
       <c r="C167" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D167">
-        <v>0.22166666666666668</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B168">
-        <v>1.8707387435064476e6</v>
+        <v>1.1688729534564952e6</v>
       </c>
       <c r="C168" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D168">
-        <v>0.23916666666666667</v>
+        <v>8.21</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B169">
-        <v>2.0219226265206872e6</v>
+        <v>1.3200962798196336e6</v>
       </c>
       <c r="C169" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D169">
-        <v>0.10583333333333333</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B170">
-        <v>574821.031096038</v>
+        <v>1.5144825795838374e6</v>
       </c>
       <c r="C170" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D170">
-        <v>2.441666666666667</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B171">
-        <v>769181.1158093434</v>
+        <v>1.6872774223094333e6</v>
       </c>
       <c r="C171" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D171">
-        <v>3.2416666666666667</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B172">
-        <v>1.2011474935592408e6</v>
+        <v>1.7736884005452667e6</v>
       </c>
       <c r="C172" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D172">
-        <v>3.3166666666666664</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B173">
-        <v>1.4171235345618173e6</v>
+        <v>2.0544912822568144e6</v>
       </c>
       <c r="C173" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D173">
-        <v>3.6166666666666667</v>
+        <v>8.38</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B174">
-        <v>1.6547069553399715e6</v>
+        <v>391161.80289477075</v>
       </c>
       <c r="C174" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D174">
-        <v>3.516666666666667</v>
+        <v>699.0</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B175">
-        <v>1.8707387435064476e6</v>
+        <v>499324.43792375014</v>
       </c>
       <c r="C175" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D175">
-        <v>3.4916666666666667</v>
+        <v>641.0</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B176">
-        <v>2.0219226265206872e6</v>
+        <v>650528.4058831015</v>
       </c>
       <c r="C176" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D176">
-        <v>3.533333333333333</v>
+        <v>955.0</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B177">
-        <v>391032.08745753707</v>
+        <v>823321.7715896445</v>
       </c>
       <c r="C177" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D177">
-        <v>0.750160690647482</v>
+        <v>879.0</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B178">
-        <v>499224.7790934134</v>
+        <v>888141.3654190782</v>
       </c>
       <c r="C178" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D178">
-        <v>0.6913592517985612</v>
+        <v>846.0</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B179">
-        <v>650415.7359801112</v>
+        <v>1.0824443668921639e6</v>
       </c>
       <c r="C179" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D179">
-        <v>0.45034618705035984</v>
+        <v>765.0</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B180">
-        <v>823212.6847922642</v>
+        <v>1.1688729534564952e6</v>
       </c>
       <c r="C180" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D180">
-        <v>0.343915582733813</v>
+        <v>867.0</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B181">
-        <v>909615.7359801112</v>
+        <v>1.3200962798196336e6</v>
       </c>
       <c r="C181" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D181">
-        <v>0.3039306043165468</v>
+        <v>853.0</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B182">
-        <v>1.0824119190816395e6</v>
+        <v>1.5144825795838374e6</v>
       </c>
       <c r="C182" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D182">
-        <v>0.18931149928057556</v>
+        <v>823.0</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B183">
-        <v>1.168767088649534e6</v>
+        <v>1.6872774223094333e6</v>
       </c>
       <c r="C183" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D183">
-        <v>0.17613997697841727</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B184">
-        <v>1.2551405049737038e6</v>
+        <v>1.7736884005452667e6</v>
       </c>
       <c r="C184" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D184">
-        <v>0.14815049208633096</v>
+        <v>711.0</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B185">
-        <v>1.341541383546906e6</v>
+        <v>2.0544912822568144e6</v>
       </c>
       <c r="C185" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D185">
-        <v>0.1300396489208633</v>
+        <v>675.0</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3061,13 +3067,13 @@
         <v>3</v>
       </c>
       <c r="B186">
-        <v>1.5143226265206872e6</v>
+        <v>391032.08745753707</v>
       </c>
       <c r="C186" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D186">
-        <v>0.0459754417266187</v>
+        <v>0.8296774193548386</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3075,13 +3081,13 @@
         <v>3</v>
       </c>
       <c r="B187">
-        <v>1.557530744903275e6</v>
+        <v>499224.7790934134</v>
       </c>
       <c r="C187" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D187">
-        <v>0.03368594100719424</v>
+        <v>0.8370967741935483</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3089,13 +3095,13 @@
         <v>3</v>
       </c>
       <c r="B188">
-        <v>1.579087933114048e6</v>
+        <v>650415.7359801112</v>
       </c>
       <c r="C188" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D188">
-        <v>0.02898182589928058</v>
+        <v>0.9064516129032258</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3103,13 +3109,13 @@
         <v>3</v>
       </c>
       <c r="B189">
-        <v>1.600714385647834e6</v>
+        <v>823212.6847922642</v>
       </c>
       <c r="C189" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D189">
-        <v>0.022925277697841726</v>
+        <v>0.8887096774193549</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3117,13 +3123,13 @@
         <v>3</v>
       </c>
       <c r="B190">
-        <v>1.6223153074353987e6</v>
+        <v>909615.7359801112</v>
       </c>
       <c r="C190" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D190">
-        <v>0.019985205755395682</v>
+        <v>0.8585483870967742</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3131,13 +3137,13 @@
         <v>3</v>
       </c>
       <c r="B191">
-        <v>1.6871235345618173e6</v>
+        <v>1.0824119190816395e6</v>
       </c>
       <c r="C191" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D191">
-        <v>0.01633951654676259</v>
+        <v>1.0806451612903225</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3145,13 +3151,13 @@
         <v>3</v>
       </c>
       <c r="B192">
-        <v>1.773541383546906e6</v>
+        <v>1.168767088649534e6</v>
       </c>
       <c r="C192" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D192">
-        <v>0.015986707913669063</v>
+        <v>0.9708064516129032</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3159,13 +3165,13 @@
         <v>3</v>
       </c>
       <c r="B193">
-        <v>1.8383343144673796e6</v>
+        <v>1.2551405049737038e6</v>
       </c>
       <c r="C193" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D193">
-        <v>0.01245862158273381</v>
+        <v>1.149516129032258</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3173,13 +3179,13 @@
         <v>3</v>
       </c>
       <c r="B194">
-        <v>2.0543078896103424e6</v>
+        <v>1.341541383546906e6</v>
       </c>
       <c r="C194" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D194">
-        <v>0.011811805755395682</v>
+        <v>1.1411290322580645</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3187,13 +3193,13 @@
         <v>3</v>
       </c>
       <c r="B195">
-        <v>391032.08745753707</v>
+        <v>1.5143226265206872e6</v>
       </c>
       <c r="C195" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D195">
-        <v>0.021979166666666664</v>
+        <v>1.0816129032258064</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3201,13 +3207,13 @@
         <v>3</v>
       </c>
       <c r="B196">
-        <v>499224.7790934134</v>
+        <v>1.557530744903275e6</v>
       </c>
       <c r="C196" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D196">
-        <v>0.017291666666666667</v>
+        <v>1.0793548387096774</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3215,13 +3221,13 @@
         <v>3</v>
       </c>
       <c r="B197">
-        <v>650415.7359801112</v>
+        <v>1.579087933114048e6</v>
       </c>
       <c r="C197" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D197">
-        <v>0.015416666666666667</v>
+        <v>0.8554838709677419</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3229,13 +3235,13 @@
         <v>3</v>
       </c>
       <c r="B198">
-        <v>823212.6847922642</v>
+        <v>1.600714385647834e6</v>
       </c>
       <c r="C198" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D198">
-        <v>0.0140625</v>
+        <v>0.6135483870967742</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3243,13 +3249,13 @@
         <v>3</v>
       </c>
       <c r="B199">
-        <v>909615.7359801112</v>
+        <v>1.6223153074353987e6</v>
       </c>
       <c r="C199" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D199">
-        <v>0.0134375</v>
+        <v>0.5656451612903226</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3257,13 +3263,13 @@
         <v>3</v>
       </c>
       <c r="B200">
-        <v>1.0824119190816395e6</v>
+        <v>1.6871235345618173e6</v>
       </c>
       <c r="C200" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D200">
-        <v>0.013020833333333334</v>
+        <v>0.5512903225806451</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3271,13 +3277,13 @@
         <v>3</v>
       </c>
       <c r="B201">
-        <v>1.168767088649534e6</v>
+        <v>1.773541383546906e6</v>
       </c>
       <c r="C201" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D201">
-        <v>0.0128125</v>
+        <v>0.5954838709677419</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3285,13 +3291,13 @@
         <v>3</v>
       </c>
       <c r="B202">
-        <v>1.2551405049737038e6</v>
+        <v>1.8383343144673796e6</v>
       </c>
       <c r="C202" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D202">
-        <v>0.012708333333333334</v>
+        <v>0.5933870967741935</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3299,13 +3305,13 @@
         <v>3</v>
       </c>
       <c r="B203">
-        <v>1.341541383546906e6</v>
+        <v>1.9463226265206872e6</v>
       </c>
       <c r="C203" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D203">
-        <v>0.0146875</v>
+        <v>0.6312903225806452</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3313,13 +3319,13 @@
         <v>3</v>
       </c>
       <c r="B204">
-        <v>1.5143226265206872e6</v>
+        <v>2.0543078896103424e6</v>
       </c>
       <c r="C204" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D204">
-        <v>0.014270833333333335</v>
+        <v>0.6196774193548388</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3327,13 +3333,13 @@
         <v>3</v>
       </c>
       <c r="B205">
-        <v>1.557530744903275e6</v>
+        <v>2.0834369762544057e6</v>
       </c>
       <c r="C205" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D205">
-        <v>0.012083333333333333</v>
+        <v>0.6014285714285714</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3341,13 +3347,13 @@
         <v>3</v>
       </c>
       <c r="B206">
-        <v>1.579087933114048e6</v>
+        <v>2.112228951263744e6</v>
       </c>
       <c r="C206" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D206">
-        <v>0.011458333333333334</v>
+        <v>0.12785714285714286</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3355,13 +3361,13 @@
         <v>3</v>
       </c>
       <c r="B207">
-        <v>1.600714385647834e6</v>
+        <v>2.1410069553399715e6</v>
       </c>
       <c r="C207" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D207">
-        <v>0.012187499999999999</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3369,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="B208">
-        <v>1.6223153074353987e6</v>
+        <v>2.155472910379259e6</v>
       </c>
       <c r="C208" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D208">
-        <v>0.012291666666666666</v>
+        <v>0.09714285714285716</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3383,13 +3389,13 @@
         <v>3</v>
       </c>
       <c r="B209">
-        <v>1.6871235345618173e6</v>
+        <v>2.2138608058982217e6</v>
       </c>
       <c r="C209" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D209">
-        <v>0.011666666666666667</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3397,13 +3403,13 @@
         <v>3</v>
       </c>
       <c r="B210">
-        <v>1.773541383546906e6</v>
+        <v>2.3074225869580563e6</v>
       </c>
       <c r="C210" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D210">
-        <v>0.011458333333333334</v>
+        <v>0.04928571428571428</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3411,13 +3417,13 @@
         <v>3</v>
       </c>
       <c r="B211">
-        <v>1.8383343144673796e6</v>
+        <v>574821.031096038</v>
       </c>
       <c r="C211" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D211">
-        <v>0.011354166666666667</v>
+        <v>0.10333333333333333</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3425,13 +3431,13 @@
         <v>3</v>
       </c>
       <c r="B212">
-        <v>1.9463226265206872e6</v>
+        <v>769181.1158093434</v>
       </c>
       <c r="C212" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D212">
-        <v>0.011770833333333333</v>
+        <v>0.11583333333333333</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3439,853 +3445,2197 @@
         <v>3</v>
       </c>
       <c r="B213">
-        <v>2.0543078896103424e6</v>
+        <v>1.2011474935592408e6</v>
       </c>
       <c r="C213" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D213">
-        <v>0.011250000000000001</v>
+        <v>0.2708333333333333</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B214">
-        <v>392225.68479226425</v>
+        <v>1.4171235345618173e6</v>
       </c>
       <c r="C214" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D214">
-        <v>0.017580645161290324</v>
+        <v>0.10416666666666667</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B215">
-        <v>500316.1715818515</v>
+        <v>1.6547069553399715e6</v>
       </c>
       <c r="C215" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D215">
-        <v>0.016451612903225808</v>
+        <v>0.22166666666666668</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B216">
-        <v>651525.5718748221</v>
+        <v>1.8707387435064476e6</v>
       </c>
       <c r="C216" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D216">
-        <v>0.016129032258064516</v>
+        <v>0.23916666666666667</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B217">
-        <v>824345.5854017917</v>
+        <v>2.0219226265206872e6</v>
       </c>
       <c r="C217" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D217">
-        <v>0.016451612903225808</v>
+        <v>0.10583333333333333</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B218">
-        <v>910705.9263187263</v>
+        <v>574821.031096038</v>
       </c>
       <c r="C218" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D218">
-        <v>0.016129032258064516</v>
+        <v>2.441666666666667</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B219">
-        <v>1.083511717430472e6</v>
+        <v>769181.1158093434</v>
       </c>
       <c r="C219" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D219">
-        <v>0.0</v>
+        <v>3.2416666666666667</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B220">
-        <v>1.1697227534325472e6</v>
+        <v>1.2011474935592408e6</v>
       </c>
       <c r="C220" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D220">
-        <v>0.015806451612903224</v>
+        <v>3.3166666666666664</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B221">
-        <v>1.2560892030163626e6</v>
+        <v>1.4171235345618173e6</v>
       </c>
       <c r="C221" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D221">
-        <v>0.016129032258064516</v>
+        <v>3.6166666666666667</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B222">
-        <v>1.3424941201017841e6</v>
+        <v>1.6547069553399715e6</v>
       </c>
       <c r="C222" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D222">
-        <v>0.01596774193548387</v>
+        <v>3.516666666666667</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B223">
-        <v>1.5152862322416226e6</v>
+        <v>1.8707387435064476e6</v>
       </c>
       <c r="C223" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D223">
-        <v>0.01596774193548387</v>
+        <v>3.4916666666666667</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B224">
-        <v>1.6016762167349702e6</v>
+        <v>2.0219226265206872e6</v>
       </c>
       <c r="C224" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D224">
-        <v>0.01596774193548387</v>
+        <v>3.533333333333333</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B225">
-        <v>1.6880587810132378e6</v>
+        <v>391032.08745753707</v>
       </c>
       <c r="C225" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D225">
-        <v>0.01596774193548387</v>
+        <v>0.750160690647482</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B226">
-        <v>1.7745283074353987e6</v>
+        <v>499224.7790934134</v>
       </c>
       <c r="C226" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D226">
-        <v>0.016774193548387096</v>
+        <v>0.6913592517985612</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B227">
-        <v>1.8393199553399715e6</v>
+        <v>650415.7359801112</v>
       </c>
       <c r="C227" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D227">
-        <v>0.01596774193548387</v>
+        <v>0.45034618705035984</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B228">
-        <v>1.9473095733201585e6</v>
+        <v>823212.6847922642</v>
       </c>
       <c r="C228" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D228">
-        <v>0.016451612903225808</v>
+        <v>0.343915582733813</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B229">
-        <v>2.05531714304388e6</v>
+        <v>909615.7359801112</v>
       </c>
       <c r="C229" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D229">
-        <v>0.0</v>
+        <v>0.3039306043165468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B230">
-        <v>575592.7855859512</v>
+        <v>1.0824119190816395e6</v>
       </c>
       <c r="C230" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D230">
-        <v>0.6575</v>
+        <v>0.18931149928057556</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B231">
-        <v>770316.1715818514</v>
+        <v>1.168767088649534e6</v>
       </c>
       <c r="C231" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D231">
-        <v>0.22999999999999998</v>
+        <v>0.17613997697841727</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B232">
-        <v>1.2021227534325472e6</v>
+        <v>1.2551405049737038e6</v>
       </c>
       <c r="C232" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D232">
-        <v>0.7875</v>
+        <v>0.14815049208633096</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B233">
-        <v>1.418075205511735e6</v>
+        <v>1.341541383546906e6</v>
       </c>
       <c r="C233" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D233">
-        <v>0.5208333333333334</v>
+        <v>0.1300396489208633</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B234">
-        <v>1.6555593691573585e6</v>
+        <v>1.5143226265206872e6</v>
       </c>
       <c r="C234" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D234">
-        <v>0.41500000000000004</v>
+        <v>0.0459754417266187</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B235">
-        <v>1.8717356265206872e6</v>
+        <v>1.557530744903275e6</v>
       </c>
       <c r="C235" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D235">
-        <v>0.9333333333333332</v>
+        <v>0.03368594100719424</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B236">
-        <v>2.022918082060749e6</v>
+        <v>1.579087933114048e6</v>
       </c>
       <c r="C236" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D236">
-        <v>0.9166666666666666</v>
+        <v>0.02898182589928058</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B237">
-        <v>575592.7855859512</v>
+        <v>1.600714385647834e6</v>
       </c>
       <c r="C237" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D237">
-        <v>1.8416666666666668</v>
+        <v>0.022925277697841726</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B238">
-        <v>770316.1715818514</v>
+        <v>1.6223153074353987e6</v>
       </c>
       <c r="C238" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D238">
-        <v>2.408333333333333</v>
+        <v>0.019985205755395682</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B239">
-        <v>1.2021227534325472e6</v>
+        <v>1.6871235345618173e6</v>
       </c>
       <c r="C239" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D239">
-        <v>2.625</v>
+        <v>0.01633951654676259</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B240">
-        <v>1.418075205511735e6</v>
+        <v>1.773541383546906e6</v>
       </c>
       <c r="C240" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D240">
-        <v>3.1833333333333336</v>
+        <v>0.015986707913669063</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B241">
-        <v>1.6555593691573585e6</v>
+        <v>1.8383343144673796e6</v>
       </c>
       <c r="C241" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D241">
-        <v>3.0583333333333336</v>
+        <v>0.01245862158273381</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B242">
-        <v>1.8717356265206872e6</v>
+        <v>2.0543078896103424e6</v>
       </c>
       <c r="C242" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D242">
-        <v>2.891666666666667</v>
+        <v>0.011811805755395682</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B243">
-        <v>2.022918082060749e6</v>
+        <v>391032.08745753707</v>
       </c>
       <c r="C243" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D243">
-        <v>2.9333333333333336</v>
+        <v>0.021979166666666664</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B244">
-        <v>392225.68479226425</v>
+        <v>499224.7790934134</v>
       </c>
       <c r="C244" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D244">
-        <v>-0.0003012906474820185</v>
+        <v>0.017291666666666667</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B245">
-        <v>500316.1715818515</v>
+        <v>650415.7359801112</v>
       </c>
       <c r="C245" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D245">
-        <v>-0.00036009208633093915</v>
+        <v>0.015416666666666667</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B246">
-        <v>651525.5718748221</v>
+        <v>823212.6847922642</v>
       </c>
       <c r="C246" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D246">
-        <v>-0.00024248920863309786</v>
+        <v>0.0140625</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B247">
-        <v>824345.5854017917</v>
+        <v>909615.7359801112</v>
       </c>
       <c r="C247" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D247">
-        <v>-0.00018368776978417678</v>
+        <v>0.0134375</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B248">
-        <v>910705.9263187263</v>
+        <v>1.0824119190816395e6</v>
       </c>
       <c r="C248" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D248">
-        <v>-0.00041889352517986</v>
+        <v>0.013020833333333334</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B249">
-        <v>1.083511717430472e6</v>
+        <v>1.168767088649534e6</v>
       </c>
       <c r="C249" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D249">
-        <v>-0.0005952978417266228</v>
+        <v>0.0128125</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B250">
-        <v>1.1697227534325472e6</v>
+        <v>1.2551405049737038e6</v>
       </c>
       <c r="C250" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D250">
-        <v>-0.0005952978417266228</v>
+        <v>0.012708333333333334</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B251">
-        <v>1.2560892030163626e6</v>
+        <v>1.341541383546906e6</v>
       </c>
       <c r="C251" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D251">
-        <v>-0.00036009208633093915</v>
+        <v>0.0146875</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B252">
-        <v>1.3424941201017841e6</v>
+        <v>1.5143226265206872e6</v>
       </c>
       <c r="C252" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D252">
-        <v>-0.0005952978417266228</v>
+        <v>0.014270833333333335</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B253">
-        <v>1.5152862322416226e6</v>
+        <v>1.557530744903275e6</v>
       </c>
       <c r="C253" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D253">
-        <v>-0.0003012906474820185</v>
+        <v>0.012083333333333333</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B254">
-        <v>1.6880587810132378e6</v>
+        <v>1.579087933114048e6</v>
       </c>
       <c r="C254" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D254">
-        <v>-0.0007129007194244645</v>
+        <v>0.011458333333333334</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B255">
-        <v>1.7745283074353987e6</v>
+        <v>1.600714385647834e6</v>
       </c>
       <c r="C255" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D255">
-        <v>-0.0005952978417266228</v>
+        <v>0.012187499999999999</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B256">
-        <v>1.8393199553399715e6</v>
+        <v>1.6223153074353987e6</v>
       </c>
       <c r="C256" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D256">
-        <v>-0.0005952978417266228</v>
+        <v>0.012291666666666666</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B257">
-        <v>2.05531714304388e6</v>
+        <v>1.6871235345618173e6</v>
       </c>
       <c r="C257" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D257">
-        <v>-0.00018368776978417678</v>
+        <v>0.011666666666666667</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B258">
-        <v>392225.68479226425</v>
+        <v>1.773541383546906e6</v>
       </c>
       <c r="C258" t="s">
         <v>8</v>
       </c>
       <c r="D258">
-        <v>0.01885416666666667</v>
+        <v>0.011458333333333334</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B259">
-        <v>500316.1715818515</v>
+        <v>1.8383343144673796e6</v>
       </c>
       <c r="C259" t="s">
         <v>8</v>
       </c>
       <c r="D259">
-        <v>0.016041666666666666</v>
+        <v>0.011354166666666667</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B260">
-        <v>651525.5718748221</v>
+        <v>1.9463226265206872e6</v>
       </c>
       <c r="C260" t="s">
         <v>8</v>
       </c>
       <c r="D260">
-        <v>0.012604166666666666</v>
+        <v>0.011770833333333333</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B261">
-        <v>824345.5854017917</v>
+        <v>2.0543078896103424e6</v>
       </c>
       <c r="C261" t="s">
         <v>8</v>
       </c>
       <c r="D261">
-        <v>0.007395833333333333</v>
+        <v>0.011250000000000001</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B262">
-        <v>910705.9263187263</v>
+        <v>391032.08745753707</v>
       </c>
       <c r="C262" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D262">
-        <v>0.011145833333333334</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B263">
-        <v>1.083511717430472e6</v>
+        <v>499224.7790934134</v>
       </c>
       <c r="C263" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D263">
-        <v>0.0</v>
+        <v>8.12</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B264">
-        <v>1.1697227534325472e6</v>
+        <v>650415.7359801112</v>
       </c>
       <c r="C264" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D264">
-        <v>0.008854166666666666</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B265">
-        <v>1.2560892030163626e6</v>
+        <v>823212.6847922642</v>
       </c>
       <c r="C265" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D265">
-        <v>0.0075</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B266">
-        <v>1.3424941201017841e6</v>
+        <v>909615.7359801112</v>
       </c>
       <c r="C266" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D266">
-        <v>0.0096875</v>
+        <v>8.05</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B267">
-        <v>1.5152862322416226e6</v>
+        <v>1.0824119190816395e6</v>
       </c>
       <c r="C267" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D267">
-        <v>0.008958333333333334</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B268">
-        <v>1.6016762167349702e6</v>
+        <v>1.168767088649534e6</v>
       </c>
       <c r="C268" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D268">
-        <v>0.0096875</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B269">
-        <v>1.6880587810132378e6</v>
+        <v>1.341541383546906e6</v>
       </c>
       <c r="C269" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D269">
-        <v>0.009479166666666667</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B270">
-        <v>1.7745283074353987e6</v>
+        <v>1.5143226265206872e6</v>
       </c>
       <c r="C270" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D270">
-        <v>0.008749999999999999</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B271">
-        <v>1.8393199553399715e6</v>
+        <v>1.6871235345618173e6</v>
       </c>
       <c r="C271" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D271">
-        <v>0.0090625</v>
+        <v>8.12</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B272">
-        <v>1.9473095733201585e6</v>
+        <v>1.773541383546906e6</v>
       </c>
       <c r="C272" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D272">
-        <v>0.0090625</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B273">
+        <v>2.0543078896103424e6</v>
+      </c>
+      <c r="C273" t="s">
+        <v>9</v>
+      </c>
+      <c r="D273">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274">
+        <v>3</v>
+      </c>
+      <c r="B274">
+        <v>391032.08745753707</v>
+      </c>
+      <c r="C274" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274">
+        <v>773.0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275">
+        <v>3</v>
+      </c>
+      <c r="B275">
+        <v>499224.7790934134</v>
+      </c>
+      <c r="C275" t="s">
+        <v>10</v>
+      </c>
+      <c r="D275">
+        <v>648.0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276">
+        <v>3</v>
+      </c>
+      <c r="B276">
+        <v>650415.7359801112</v>
+      </c>
+      <c r="C276" t="s">
+        <v>10</v>
+      </c>
+      <c r="D276">
+        <v>878.0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277">
+        <v>3</v>
+      </c>
+      <c r="B277">
+        <v>823212.6847922642</v>
+      </c>
+      <c r="C277" t="s">
+        <v>10</v>
+      </c>
+      <c r="D277">
+        <v>905.0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278">
+        <v>3</v>
+      </c>
+      <c r="B278">
+        <v>909615.7359801112</v>
+      </c>
+      <c r="C278" t="s">
+        <v>10</v>
+      </c>
+      <c r="D278">
+        <v>872.0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279">
+        <v>3</v>
+      </c>
+      <c r="B279">
+        <v>1.0824119190816395e6</v>
+      </c>
+      <c r="C279" t="s">
+        <v>10</v>
+      </c>
+      <c r="D279">
+        <v>831.0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280">
+        <v>3</v>
+      </c>
+      <c r="B280">
+        <v>1.168767088649534e6</v>
+      </c>
+      <c r="C280" t="s">
+        <v>10</v>
+      </c>
+      <c r="D280">
+        <v>876.0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281">
+        <v>3</v>
+      </c>
+      <c r="B281">
+        <v>1.341541383546906e6</v>
+      </c>
+      <c r="C281" t="s">
+        <v>10</v>
+      </c>
+      <c r="D281">
+        <v>862.0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282">
+        <v>3</v>
+      </c>
+      <c r="B282">
+        <v>1.5143226265206872e6</v>
+      </c>
+      <c r="C282" t="s">
+        <v>10</v>
+      </c>
+      <c r="D282">
+        <v>811.0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283">
+        <v>3</v>
+      </c>
+      <c r="B283">
+        <v>1.6871235345618173e6</v>
+      </c>
+      <c r="C283" t="s">
+        <v>10</v>
+      </c>
+      <c r="D283">
+        <v>749.0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284">
+        <v>3</v>
+      </c>
+      <c r="B284">
+        <v>1.773541383546906e6</v>
+      </c>
+      <c r="C284" t="s">
+        <v>10</v>
+      </c>
+      <c r="D284">
+        <v>744.0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285">
+        <v>3</v>
+      </c>
+      <c r="B285">
+        <v>2.0543078896103424e6</v>
+      </c>
+      <c r="C285" t="s">
+        <v>10</v>
+      </c>
+      <c r="D285">
+        <v>729.0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286">
+        <v>4</v>
+      </c>
+      <c r="B286">
+        <v>392225.68479226425</v>
+      </c>
+      <c r="C286" t="s">
+        <v>4</v>
+      </c>
+      <c r="D286">
+        <v>0.017580645161290324</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287">
+        <v>4</v>
+      </c>
+      <c r="B287">
+        <v>500316.1715818515</v>
+      </c>
+      <c r="C287" t="s">
+        <v>4</v>
+      </c>
+      <c r="D287">
+        <v>0.016451612903225808</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288">
+        <v>4</v>
+      </c>
+      <c r="B288">
+        <v>651525.5718748221</v>
+      </c>
+      <c r="C288" t="s">
+        <v>4</v>
+      </c>
+      <c r="D288">
+        <v>0.016129032258064516</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289">
+        <v>4</v>
+      </c>
+      <c r="B289">
+        <v>824345.5854017917</v>
+      </c>
+      <c r="C289" t="s">
+        <v>4</v>
+      </c>
+      <c r="D289">
+        <v>0.016451612903225808</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290">
+        <v>4</v>
+      </c>
+      <c r="B290">
+        <v>910705.9263187263</v>
+      </c>
+      <c r="C290" t="s">
+        <v>4</v>
+      </c>
+      <c r="D290">
+        <v>0.016129032258064516</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291">
+        <v>4</v>
+      </c>
+      <c r="B291">
+        <v>1.083511717430472e6</v>
+      </c>
+      <c r="C291" t="s">
+        <v>4</v>
+      </c>
+      <c r="D291">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292">
+        <v>4</v>
+      </c>
+      <c r="B292">
+        <v>1.1697227534325472e6</v>
+      </c>
+      <c r="C292" t="s">
+        <v>4</v>
+      </c>
+      <c r="D292">
+        <v>0.015806451612903224</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293">
+        <v>4</v>
+      </c>
+      <c r="B293">
+        <v>1.2560892030163626e6</v>
+      </c>
+      <c r="C293" t="s">
+        <v>4</v>
+      </c>
+      <c r="D293">
+        <v>0.016129032258064516</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294">
+        <v>4</v>
+      </c>
+      <c r="B294">
+        <v>1.3424941201017841e6</v>
+      </c>
+      <c r="C294" t="s">
+        <v>4</v>
+      </c>
+      <c r="D294">
+        <v>0.01596774193548387</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295">
+        <v>4</v>
+      </c>
+      <c r="B295">
+        <v>1.5152862322416226e6</v>
+      </c>
+      <c r="C295" t="s">
+        <v>4</v>
+      </c>
+      <c r="D295">
+        <v>0.01596774193548387</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296">
+        <v>4</v>
+      </c>
+      <c r="B296">
+        <v>1.6016762167349702e6</v>
+      </c>
+      <c r="C296" t="s">
+        <v>4</v>
+      </c>
+      <c r="D296">
+        <v>0.01596774193548387</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297">
+        <v>4</v>
+      </c>
+      <c r="B297">
+        <v>1.6880587810132378e6</v>
+      </c>
+      <c r="C297" t="s">
+        <v>4</v>
+      </c>
+      <c r="D297">
+        <v>0.01596774193548387</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298">
+        <v>4</v>
+      </c>
+      <c r="B298">
+        <v>1.7745283074353987e6</v>
+      </c>
+      <c r="C298" t="s">
+        <v>4</v>
+      </c>
+      <c r="D298">
+        <v>0.016774193548387096</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299">
+        <v>4</v>
+      </c>
+      <c r="B299">
+        <v>1.8393199553399715e6</v>
+      </c>
+      <c r="C299" t="s">
+        <v>4</v>
+      </c>
+      <c r="D299">
+        <v>0.01596774193548387</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300">
+        <v>4</v>
+      </c>
+      <c r="B300">
+        <v>1.9473095733201585e6</v>
+      </c>
+      <c r="C300" t="s">
+        <v>4</v>
+      </c>
+      <c r="D300">
+        <v>0.016451612903225808</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301">
+        <v>4</v>
+      </c>
+      <c r="B301">
         <v>2.05531714304388e6</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C301" t="s">
+        <v>4</v>
+      </c>
+      <c r="D301">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302">
+        <v>4</v>
+      </c>
+      <c r="B302">
+        <v>575592.7855859512</v>
+      </c>
+      <c r="C302" t="s">
+        <v>5</v>
+      </c>
+      <c r="D302">
+        <v>0.6575</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303">
+        <v>4</v>
+      </c>
+      <c r="B303">
+        <v>770316.1715818514</v>
+      </c>
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303">
+        <v>0.22999999999999998</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304">
+        <v>4</v>
+      </c>
+      <c r="B304">
+        <v>1.2021227534325472e6</v>
+      </c>
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+      <c r="D304">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305">
+        <v>4</v>
+      </c>
+      <c r="B305">
+        <v>1.418075205511735e6</v>
+      </c>
+      <c r="C305" t="s">
+        <v>5</v>
+      </c>
+      <c r="D305">
+        <v>0.5208333333333334</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306">
+        <v>4</v>
+      </c>
+      <c r="B306">
+        <v>1.6555593691573585e6</v>
+      </c>
+      <c r="C306" t="s">
+        <v>5</v>
+      </c>
+      <c r="D306">
+        <v>0.41500000000000004</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307">
+        <v>4</v>
+      </c>
+      <c r="B307">
+        <v>1.8717356265206872e6</v>
+      </c>
+      <c r="C307" t="s">
+        <v>5</v>
+      </c>
+      <c r="D307">
+        <v>0.9333333333333332</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308">
+        <v>4</v>
+      </c>
+      <c r="B308">
+        <v>2.022918082060749e6</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309">
+        <v>4</v>
+      </c>
+      <c r="B309">
+        <v>575592.7855859512</v>
+      </c>
+      <c r="C309" t="s">
+        <v>6</v>
+      </c>
+      <c r="D309">
+        <v>1.8416666666666668</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310">
+        <v>4</v>
+      </c>
+      <c r="B310">
+        <v>770316.1715818514</v>
+      </c>
+      <c r="C310" t="s">
+        <v>6</v>
+      </c>
+      <c r="D310">
+        <v>2.408333333333333</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311">
+        <v>4</v>
+      </c>
+      <c r="B311">
+        <v>1.2021227534325472e6</v>
+      </c>
+      <c r="C311" t="s">
+        <v>6</v>
+      </c>
+      <c r="D311">
+        <v>2.625</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312">
+        <v>4</v>
+      </c>
+      <c r="B312">
+        <v>1.418075205511735e6</v>
+      </c>
+      <c r="C312" t="s">
+        <v>6</v>
+      </c>
+      <c r="D312">
+        <v>3.1833333333333336</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313">
+        <v>4</v>
+      </c>
+      <c r="B313">
+        <v>1.6555593691573585e6</v>
+      </c>
+      <c r="C313" t="s">
+        <v>6</v>
+      </c>
+      <c r="D313">
+        <v>3.0583333333333336</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314">
+        <v>4</v>
+      </c>
+      <c r="B314">
+        <v>1.8717356265206872e6</v>
+      </c>
+      <c r="C314" t="s">
+        <v>6</v>
+      </c>
+      <c r="D314">
+        <v>2.891666666666667</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315">
+        <v>4</v>
+      </c>
+      <c r="B315">
+        <v>2.022918082060749e6</v>
+      </c>
+      <c r="C315" t="s">
+        <v>6</v>
+      </c>
+      <c r="D315">
+        <v>2.9333333333333336</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316">
+        <v>4</v>
+      </c>
+      <c r="B316">
+        <v>392225.68479226425</v>
+      </c>
+      <c r="C316" t="s">
+        <v>7</v>
+      </c>
+      <c r="D316">
+        <v>-0.0003012906474820185</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317">
+        <v>4</v>
+      </c>
+      <c r="B317">
+        <v>500316.1715818515</v>
+      </c>
+      <c r="C317" t="s">
+        <v>7</v>
+      </c>
+      <c r="D317">
+        <v>-0.00036009208633093915</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318">
+        <v>4</v>
+      </c>
+      <c r="B318">
+        <v>651525.5718748221</v>
+      </c>
+      <c r="C318" t="s">
+        <v>7</v>
+      </c>
+      <c r="D318">
+        <v>-0.00024248920863309786</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319">
+        <v>4</v>
+      </c>
+      <c r="B319">
+        <v>824345.5854017917</v>
+      </c>
+      <c r="C319" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319">
+        <v>-0.00018368776978417678</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320">
+        <v>4</v>
+      </c>
+      <c r="B320">
+        <v>910705.9263187263</v>
+      </c>
+      <c r="C320" t="s">
+        <v>7</v>
+      </c>
+      <c r="D320">
+        <v>-0.00041889352517986</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321">
+        <v>4</v>
+      </c>
+      <c r="B321">
+        <v>1.083511717430472e6</v>
+      </c>
+      <c r="C321" t="s">
+        <v>7</v>
+      </c>
+      <c r="D321">
+        <v>-0.0005952978417266228</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322">
+        <v>4</v>
+      </c>
+      <c r="B322">
+        <v>1.1697227534325472e6</v>
+      </c>
+      <c r="C322" t="s">
+        <v>7</v>
+      </c>
+      <c r="D322">
+        <v>-0.0005952978417266228</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323">
+        <v>4</v>
+      </c>
+      <c r="B323">
+        <v>1.2560892030163626e6</v>
+      </c>
+      <c r="C323" t="s">
+        <v>7</v>
+      </c>
+      <c r="D323">
+        <v>-0.00036009208633093915</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324">
+        <v>4</v>
+      </c>
+      <c r="B324">
+        <v>1.3424941201017841e6</v>
+      </c>
+      <c r="C324" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324">
+        <v>-0.0005952978417266228</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325">
+        <v>4</v>
+      </c>
+      <c r="B325">
+        <v>1.5152862322416226e6</v>
+      </c>
+      <c r="C325" t="s">
+        <v>7</v>
+      </c>
+      <c r="D325">
+        <v>-0.0003012906474820185</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326">
+        <v>4</v>
+      </c>
+      <c r="B326">
+        <v>1.6880587810132378e6</v>
+      </c>
+      <c r="C326" t="s">
+        <v>7</v>
+      </c>
+      <c r="D326">
+        <v>-0.0007129007194244645</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327">
+        <v>4</v>
+      </c>
+      <c r="B327">
+        <v>1.7745283074353987e6</v>
+      </c>
+      <c r="C327" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327">
+        <v>-0.0005952978417266228</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328">
+        <v>4</v>
+      </c>
+      <c r="B328">
+        <v>1.8393199553399715e6</v>
+      </c>
+      <c r="C328" t="s">
+        <v>7</v>
+      </c>
+      <c r="D328">
+        <v>-0.0005952978417266228</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329">
+        <v>4</v>
+      </c>
+      <c r="B329">
+        <v>2.05531714304388e6</v>
+      </c>
+      <c r="C329" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329">
+        <v>-0.00018368776978417678</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330">
+        <v>4</v>
+      </c>
+      <c r="B330">
+        <v>392225.68479226425</v>
+      </c>
+      <c r="C330" t="s">
         <v>8</v>
       </c>
-      <c r="D273">
+      <c r="D330">
+        <v>0.01885416666666667</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331">
+        <v>4</v>
+      </c>
+      <c r="B331">
+        <v>500316.1715818515</v>
+      </c>
+      <c r="C331" t="s">
+        <v>8</v>
+      </c>
+      <c r="D331">
+        <v>0.016041666666666666</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332">
+        <v>4</v>
+      </c>
+      <c r="B332">
+        <v>651525.5718748221</v>
+      </c>
+      <c r="C332" t="s">
+        <v>8</v>
+      </c>
+      <c r="D332">
+        <v>0.012604166666666666</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333">
+        <v>4</v>
+      </c>
+      <c r="B333">
+        <v>824345.5854017917</v>
+      </c>
+      <c r="C333" t="s">
+        <v>8</v>
+      </c>
+      <c r="D333">
+        <v>0.007395833333333333</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334">
+        <v>4</v>
+      </c>
+      <c r="B334">
+        <v>910705.9263187263</v>
+      </c>
+      <c r="C334" t="s">
+        <v>8</v>
+      </c>
+      <c r="D334">
+        <v>0.011145833333333334</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335">
+        <v>4</v>
+      </c>
+      <c r="B335">
+        <v>1.083511717430472e6</v>
+      </c>
+      <c r="C335" t="s">
+        <v>8</v>
+      </c>
+      <c r="D335">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336">
+        <v>4</v>
+      </c>
+      <c r="B336">
+        <v>1.1697227534325472e6</v>
+      </c>
+      <c r="C336" t="s">
+        <v>8</v>
+      </c>
+      <c r="D336">
+        <v>0.008854166666666666</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337">
+        <v>4</v>
+      </c>
+      <c r="B337">
+        <v>1.2560892030163626e6</v>
+      </c>
+      <c r="C337" t="s">
+        <v>8</v>
+      </c>
+      <c r="D337">
+        <v>0.0075</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338">
+        <v>4</v>
+      </c>
+      <c r="B338">
+        <v>1.3424941201017841e6</v>
+      </c>
+      <c r="C338" t="s">
+        <v>8</v>
+      </c>
+      <c r="D338">
+        <v>0.0096875</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339">
+        <v>4</v>
+      </c>
+      <c r="B339">
+        <v>1.5152862322416226e6</v>
+      </c>
+      <c r="C339" t="s">
+        <v>8</v>
+      </c>
+      <c r="D339">
+        <v>0.008958333333333334</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340">
+        <v>4</v>
+      </c>
+      <c r="B340">
+        <v>1.6016762167349702e6</v>
+      </c>
+      <c r="C340" t="s">
+        <v>8</v>
+      </c>
+      <c r="D340">
+        <v>0.0096875</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341">
+        <v>4</v>
+      </c>
+      <c r="B341">
+        <v>1.6880587810132378e6</v>
+      </c>
+      <c r="C341" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341">
+        <v>0.009479166666666667</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
+      <c r="A342">
+        <v>4</v>
+      </c>
+      <c r="B342">
+        <v>1.7745283074353987e6</v>
+      </c>
+      <c r="C342" t="s">
+        <v>8</v>
+      </c>
+      <c r="D342">
+        <v>0.008749999999999999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
+      <c r="A343">
+        <v>4</v>
+      </c>
+      <c r="B343">
+        <v>1.8393199553399715e6</v>
+      </c>
+      <c r="C343" t="s">
+        <v>8</v>
+      </c>
+      <c r="D343">
+        <v>0.0090625</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
+      <c r="A344">
+        <v>4</v>
+      </c>
+      <c r="B344">
+        <v>1.9473095733201585e6</v>
+      </c>
+      <c r="C344" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344">
+        <v>0.0090625</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
+      <c r="A345">
+        <v>4</v>
+      </c>
+      <c r="B345">
+        <v>2.05531714304388e6</v>
+      </c>
+      <c r="C345" t="s">
+        <v>8</v>
+      </c>
+      <c r="D345">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
+      <c r="A346">
+        <v>4</v>
+      </c>
+      <c r="B346">
+        <v>392225.68479226425</v>
+      </c>
+      <c r="C346" t="s">
+        <v>9</v>
+      </c>
+      <c r="D346">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
+      <c r="A347">
+        <v>4</v>
+      </c>
+      <c r="B347">
+        <v>500316.1715818515</v>
+      </c>
+      <c r="C347" t="s">
+        <v>9</v>
+      </c>
+      <c r="D347">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
+      <c r="A348">
+        <v>4</v>
+      </c>
+      <c r="B348">
+        <v>651525.5718748221</v>
+      </c>
+      <c r="C348" t="s">
+        <v>9</v>
+      </c>
+      <c r="D348">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
+      <c r="A349">
+        <v>4</v>
+      </c>
+      <c r="B349">
+        <v>824345.5854017917</v>
+      </c>
+      <c r="C349" t="s">
+        <v>9</v>
+      </c>
+      <c r="D349">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
+      <c r="A350">
+        <v>4</v>
+      </c>
+      <c r="B350">
+        <v>910705.9263187263</v>
+      </c>
+      <c r="C350" t="s">
+        <v>9</v>
+      </c>
+      <c r="D350">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
+      <c r="A351">
+        <v>4</v>
+      </c>
+      <c r="B351">
+        <v>1.083511717430472e6</v>
+      </c>
+      <c r="C351" t="s">
+        <v>9</v>
+      </c>
+      <c r="D351">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
+      <c r="A352">
+        <v>4</v>
+      </c>
+      <c r="B352">
+        <v>1.1697227534325472e6</v>
+      </c>
+      <c r="C352" t="s">
+        <v>9</v>
+      </c>
+      <c r="D352">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353">
+        <v>4</v>
+      </c>
+      <c r="B353">
+        <v>1.3424941201017841e6</v>
+      </c>
+      <c r="C353" t="s">
+        <v>9</v>
+      </c>
+      <c r="D353">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
+      <c r="A354">
+        <v>4</v>
+      </c>
+      <c r="B354">
+        <v>1.5152862322416226e6</v>
+      </c>
+      <c r="C354" t="s">
+        <v>9</v>
+      </c>
+      <c r="D354">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355">
+        <v>4</v>
+      </c>
+      <c r="B355">
+        <v>1.6880587810132378e6</v>
+      </c>
+      <c r="C355" t="s">
+        <v>9</v>
+      </c>
+      <c r="D355">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356">
+        <v>4</v>
+      </c>
+      <c r="B356">
+        <v>1.7745283074353987e6</v>
+      </c>
+      <c r="C356" t="s">
+        <v>9</v>
+      </c>
+      <c r="D356">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357">
+        <v>4</v>
+      </c>
+      <c r="B357">
+        <v>2.05531714304388e6</v>
+      </c>
+      <c r="C357" t="s">
+        <v>9</v>
+      </c>
+      <c r="D357">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
+      <c r="A358">
+        <v>4</v>
+      </c>
+      <c r="B358">
+        <v>392225.68479226425</v>
+      </c>
+      <c r="C358" t="s">
+        <v>10</v>
+      </c>
+      <c r="D358">
+        <v>473.0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359">
+        <v>4</v>
+      </c>
+      <c r="B359">
+        <v>500316.1715818515</v>
+      </c>
+      <c r="C359" t="s">
+        <v>10</v>
+      </c>
+      <c r="D359">
+        <v>484.0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360">
+        <v>4</v>
+      </c>
+      <c r="B360">
+        <v>651525.5718748221</v>
+      </c>
+      <c r="C360" t="s">
+        <v>10</v>
+      </c>
+      <c r="D360">
+        <v>621.0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361">
+        <v>4</v>
+      </c>
+      <c r="B361">
+        <v>824345.5854017917</v>
+      </c>
+      <c r="C361" t="s">
+        <v>10</v>
+      </c>
+      <c r="D361">
+        <v>583.0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362">
+        <v>4</v>
+      </c>
+      <c r="B362">
+        <v>910705.9263187263</v>
+      </c>
+      <c r="C362" t="s">
+        <v>10</v>
+      </c>
+      <c r="D362">
+        <v>635.0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
+      <c r="A363">
+        <v>4</v>
+      </c>
+      <c r="B363">
+        <v>1.083511717430472e6</v>
+      </c>
+      <c r="C363" t="s">
+        <v>10</v>
+      </c>
+      <c r="D363">
+        <v>639.0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364">
+        <v>4</v>
+      </c>
+      <c r="B364">
+        <v>1.1697227534325472e6</v>
+      </c>
+      <c r="C364" t="s">
+        <v>10</v>
+      </c>
+      <c r="D364">
+        <v>608.0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365">
+        <v>4</v>
+      </c>
+      <c r="B365">
+        <v>1.3424941201017841e6</v>
+      </c>
+      <c r="C365" t="s">
+        <v>10</v>
+      </c>
+      <c r="D365">
+        <v>557.0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366">
+        <v>4</v>
+      </c>
+      <c r="B366">
+        <v>1.5152862322416226e6</v>
+      </c>
+      <c r="C366" t="s">
+        <v>10</v>
+      </c>
+      <c r="D366">
+        <v>598.0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367">
+        <v>4</v>
+      </c>
+      <c r="B367">
+        <v>1.6880587810132378e6</v>
+      </c>
+      <c r="C367" t="s">
+        <v>10</v>
+      </c>
+      <c r="D367">
+        <v>548.0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368">
+        <v>4</v>
+      </c>
+      <c r="B368">
+        <v>1.7745283074353987e6</v>
+      </c>
+      <c r="C368" t="s">
+        <v>10</v>
+      </c>
+      <c r="D368">
+        <v>573.0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369">
+        <v>4</v>
+      </c>
+      <c r="B369">
+        <v>2.05531714304388e6</v>
+      </c>
+      <c r="C369" t="s">
+        <v>10</v>
+      </c>
+      <c r="D369">
+        <v>569.0</v>
       </c>
     </row>
   </sheetData>
@@ -4306,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4555,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5206,57 +6556,57 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
